--- a/OCT_2026/10-22-26/Euro ok.xlsx
+++ b/OCT_2026/10-22-26/Euro ok.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E3291B-D280-46A4-8E35-B2AB55715421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C2D4A2E-C207-4591-B300-C4D5548E96A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="871" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="871" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dist Price List (2)" sheetId="41" state="hidden" r:id="rId1"/>
@@ -47912,7 +47912,7 @@
       <c r="L4" s="393"/>
       <c r="M4" s="396">
         <f ca="1">TODAY()+1</f>
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="N4" s="396"/>
       <c r="O4" s="396"/>
@@ -47940,7 +47940,7 @@
       <c r="L5" s="393"/>
       <c r="M5" s="396">
         <f ca="1">M4-1</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="N5" s="392"/>
       <c r="O5" s="392"/>
@@ -54135,7 +54135,7 @@
       <c r="G3" s="388"/>
       <c r="H3" s="385">
         <f ca="1">TODAY()</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="I3" s="385"/>
       <c r="J3" s="386"/>
@@ -59218,10 +59218,6 @@
         <v>6155.6180501694917</v>
       </c>
       <c r="Q20" s="156"/>
-      <c r="R20">
-        <f>P20/21</f>
-        <v>293.12466905569011</v>
-      </c>
       <c r="S20" s="269">
         <f>+S19</f>
         <v>0.1</v>
